--- a/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>32,49; 44,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>40,6; 52,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>45,68; 57,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>53,65; 66,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>78,5; 87,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>82,63; 90,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>85,0; 92,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>86,21; 94,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>56,1; 64,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>62,64; 70,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>66,19; 74,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>71,05; 78,94</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>33,61; 42,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>33,53; 41,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>42,86; 52,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>66,9; 77,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>80,39; 86,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>80,18; 87,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>82,53; 88,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>88,39; 93,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>57,67; 64,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>58,22; 64,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>63,81; 69,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,17</t>
+          <t>78,58; 84,9</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>23,83; 33,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>36,2; 46,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>53,71; 64,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>72,27; 80,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>78,93; 86,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>79,72; 87,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>86,32; 92,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>86,41; 92,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>52,5; 60,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>59,39; 67,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>71,82; 78,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>80,56; 85,93</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>25,33; 35,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>43,46; 54,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>46,49; 56,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>57,58; 71,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>77,94; 86,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>79,29; 87,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>78,72; 86,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>86,01; 94,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>53,18; 60,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>62,89; 70,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>64,42; 71,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>75,95; 85,69</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>29,49; 43,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>24,1; 37,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>50,75; 64,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>83,75; 91,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>81,63; 90,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>74,54; 84,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>88,67; 95,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>92,16; 97,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>57,24; 66,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>50,66; 60,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>71,49; 79,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>89,86; 95,37</t>
         </is>
       </c>
     </row>
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>21,88; 32,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>37,12; 49,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>37,87; 50,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>71,83; 81,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>83,05; 91,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>81,92; 89,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>82,94; 91,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>88,98; 94,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>53,28; 61,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>60,9; 69,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>62,17; 70,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>81,37; 86,84</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>36,56; 44,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>41,8; 50,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>48,13; 56,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>68,32; 76,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>83,68; 88,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>79,21; 85,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>84,18; 89,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>86,55; 95,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>61,22; 66,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>61,44; 67,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>67,52; 72,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>79,0; 89,27</t>
         </is>
       </c>
     </row>
@@ -1629,62 +1629,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>27,49; 34,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>43,07; 50,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>54,75; 62,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>14,31; 44,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>78,96; 84,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>80,07; 85,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>84,63; 89,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>90,73; 94,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>54,51; 59,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>62,57; 67,94</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>70,87; 75,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>36,26; 69,47</t>
         </is>
       </c>
     </row>
@@ -1769,62 +1769,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>32,51; 35,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>41,96; 45,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>51,22; 54,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>46,73; 66,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,71; 85,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,28; 84,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>86,21; 88,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,04</t>
+          <t>90,37; 93,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>58,32; 60,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>62,82; 65,2</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>69,55; 71,68</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,02</t>
+          <t>68,12; 80,32</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2073,62 +2073,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>221</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>502</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>685</t>
         </is>
       </c>
     </row>
@@ -2141,62 +2141,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104826</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136890</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217129</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250032</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>258376</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>264925</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>321955</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>408712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>451513</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>88710; 121924</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>119673; 154966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>134189; 169319</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1801</t>
+          <t>167074; 206429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2035</t>
+          <t>203968; 228161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2145</t>
+          <t>237347; 260528</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>245393; 267531</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1032</t>
+          <t>249691; 273876</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1983</t>
+          <t>298938; 344410</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2073</t>
+          <t>364556; 410673</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2056</t>
+          <t>385562; 432174</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1327</t>
+          <t>427060; 474473</t>
         </is>
       </c>
     </row>
@@ -2281,62 +2281,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>402</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>954</t>
         </is>
       </c>
     </row>
@@ -2349,62 +2349,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187867</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>375996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>422067</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438881</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>449363</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471212</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>609934</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628398</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>685536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>847208</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2031</t>
+          <t>165735; 210854</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2052</t>
+          <t>169157; 210732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>213820; 259980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2598</t>
+          <t>346819; 401491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1935</t>
+          <t>405116; 436712</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>419933; 456415</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>430915; 464124</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1377</t>
+          <t>455200; 483614</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>575021; 641642</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2074</t>
+          <t>598672; 663053</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2051</t>
+          <t>651498; 712384</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 1804</t>
+          <t>812061; 877282</t>
         </is>
       </c>
     </row>
@@ -2489,62 +2489,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>265</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>477</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>745</t>
         </is>
       </c>
     </row>
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90966</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134936</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>242148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>279030</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285838</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302520</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311471</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369996</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>420774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>553619</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>75989; 107839</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1944</t>
+          <t>117293; 151427</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1821</t>
+          <t>170705; 203458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1682</t>
+          <t>227949; 255290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>264740; 291772</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2058</t>
+          <t>271863; 298588</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>290298; 312225</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1248</t>
+          <t>300583; 320661</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1945</t>
+          <t>343511; 393732</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>394989; 447831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>469817; 511374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 1425</t>
+          <t>534332; 569993</t>
         </is>
       </c>
     </row>
@@ -2697,62 +2697,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>541</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>418</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>729</t>
         </is>
       </c>
     </row>
@@ -2765,62 +2765,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108606</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>182266</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>190119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305293</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324806</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320816</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430401</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>413899</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>507072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>510935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633330</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>90842; 127360</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2081</t>
+          <t>162551; 202510</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>171107; 209321</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>179981; 223721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1851</t>
+          <t>288633; 318597</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>308387; 338586</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>304871; 335372</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1522</t>
+          <t>409158; 449595</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>387688; 441154</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>479846; 534137</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>486582; 536939</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1697</t>
+          <t>598681; 675463</t>
         </is>
       </c>
     </row>
@@ -2905,62 +2905,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>474</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>718</t>
         </is>
       </c>
     </row>
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73348</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64587</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>121343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>157093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180063</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>176268</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202792</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>247405</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253411</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324135</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>404498</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1885</t>
+          <t>59957; 87974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>51241; 79064</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>107188; 136300</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1226</t>
+          <t>149298; 163448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>169520; 188585</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1978</t>
+          <t>163675; 186554</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>192972; 208648</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1002</t>
+          <t>238500; 253181</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>235236; 273386</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>218965; 260935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 1893</t>
+          <t>306570; 340528</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 1084</t>
+          <t>392750; 416839</t>
         </is>
       </c>
     </row>
@@ -3113,62 +3113,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>308</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>342</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>693</t>
         </is>
       </c>
     </row>
@@ -3181,62 +3181,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72594</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119007</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243429</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241529</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238958</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>235819</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>316024</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>354085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>443393</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1947</t>
+          <t>59244; 88462</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>101710; 136001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1938</t>
+          <t>99018; 131297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1391</t>
+          <t>193669; 219858</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>231006; 253765</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>229401; 252000</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>225661; 249212</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1071</t>
+          <t>228734; 241805</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>292495; 338093</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>337398; 384177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>331720; 376250</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1216</t>
+          <t>428595; 457375</t>
         </is>
       </c>
     </row>
@@ -3321,62 +3321,62 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>563</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>865</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>770</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1311</t>
         </is>
       </c>
     </row>
@@ -3389,62 +3389,62 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>251213</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>304200</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>344190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>452810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549368</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572086</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599461</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>769182</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800581</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>876287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>943651</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1221992</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>224878; 274426</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2056</t>
+          <t>277016; 333735</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2170</t>
+          <t>315510; 370261</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>426531; 480536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>532068; 564983</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>549614; 593526</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2052</t>
+          <t>580253; 615174</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 1697</t>
+          <t>735039; 813207</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1972</t>
+          <t>765742; 833868</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2076</t>
+          <t>833487; 909502</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2110</t>
+          <t>907922; 977889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 1814</t>
+          <t>1164053; 1315381</t>
         </is>
       </c>
     </row>
@@ -3529,62 +3529,62 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>434</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>326</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>660</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>831</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1329</t>
         </is>
       </c>
     </row>
@@ -3597,62 +3597,62 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>230916</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>364437</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>453424</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>295470</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640905</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>681381</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>721082</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667162</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>871822</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1045818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1174506</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962632</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1938</t>
+          <t>204202; 258484</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2084</t>
+          <t>335549; 394881</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>426311; 484187</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2337</t>
+          <t>132880; 414247</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>618632; 661390</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>658084; 701322</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>699215; 739828</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 1297</t>
+          <t>651164; 679863</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>832044; 909991</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>1001669; 1087628</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>1137210; 1210880</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 1733</t>
+          <t>596991; 1143817</t>
         </is>
       </c>
     </row>
@@ -3737,62 +3737,62 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7164</t>
         </is>
       </c>
     </row>
@@ -3805,62 +3805,62 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1120336</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1495841</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1798474</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2120608</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2837285</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2970821</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3093366</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3397577</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3957622</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4466662</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4891842</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5518185</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>1064943; 1177799</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 2050</t>
+          <t>1437310; 1559799</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>1734100; 1856067</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>1616269; 2302431</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>2791090; 2877241</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>2926098; 3019903</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>3051482; 3135285</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 1328</t>
+          <t>3353826; 3455773</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>3878149; 4043597</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0; 2062</t>
+          <t>4386140; 4552176</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0; 2028</t>
+          <t>4816483; 4963963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0; 1576</t>
+          <t>4883769; 5758566</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,49; 44,66</t>
+          <t>32,27; 44,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,6; 52,58</t>
+          <t>39,93; 52,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,68; 57,64</t>
+          <t>45,08; 56,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,65; 66,28</t>
+          <t>51,79; 63,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,5; 87,81</t>
+          <t>78,35; 87,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,63; 90,7</t>
+          <t>82,3; 90,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,0; 92,67</t>
+          <t>85,3; 93,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,21; 94,56</t>
+          <t>87,73; 94,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,1; 64,64</t>
+          <t>55,87; 64,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,64; 70,56</t>
+          <t>62,25; 70,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66,19; 74,2</t>
+          <t>66,55; 73,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,05; 78,94</t>
+          <t>70,86; 77,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,61; 42,76</t>
+          <t>33,93; 43,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,53; 41,77</t>
+          <t>33,31; 42,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,86; 52,11</t>
+          <t>42,93; 51,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,9; 77,45</t>
+          <t>68,2; 78,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,39; 86,66</t>
+          <t>80,29; 86,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,18; 87,14</t>
+          <t>80,12; 86,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,53; 88,89</t>
+          <t>82,86; 89,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,39; 93,91</t>
+          <t>87,76; 93,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,67; 64,36</t>
+          <t>58,14; 64,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,22; 64,48</t>
+          <t>57,5; 64,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63,81; 69,77</t>
+          <t>63,87; 70,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,58; 84,9</t>
+          <t>79,18; 84,97</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,82</t>
+          <t>23,81; 34,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,2; 46,73</t>
+          <t>36,26; 46,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,71; 64,02</t>
+          <t>53,54; 64,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72,27; 80,94</t>
+          <t>71,38; 80,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,93; 86,99</t>
+          <t>78,9; 86,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,72; 87,56</t>
+          <t>79,56; 87,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,32; 92,84</t>
+          <t>86,2; 92,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,41; 92,18</t>
+          <t>86,76; 92,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,5; 60,18</t>
+          <t>52,43; 60,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59,39; 67,34</t>
+          <t>59,22; 66,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71,82; 78,18</t>
+          <t>71,53; 77,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,56; 85,93</t>
+          <t>80,66; 85,93</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,33; 35,51</t>
+          <t>25,44; 35,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,46; 54,15</t>
+          <t>43,42; 53,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,49; 56,87</t>
+          <t>46,59; 57,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,58; 71,58</t>
+          <t>57,48; 71,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,94; 86,04</t>
+          <t>78,57; 85,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,29; 87,05</t>
+          <t>79,34; 87,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,72; 86,6</t>
+          <t>78,66; 86,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,01; 94,51</t>
+          <t>83,72; 91,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,18; 60,52</t>
+          <t>53,23; 60,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62,89; 70,01</t>
+          <t>62,99; 69,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64,42; 71,09</t>
+          <t>64,21; 70,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,95; 85,69</t>
+          <t>73,1; 80,88</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,49; 43,27</t>
+          <t>28,74; 42,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,1; 37,19</t>
+          <t>24,7; 37,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,75; 64,53</t>
+          <t>50,47; 63,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,75; 91,68</t>
+          <t>83,63; 91,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,63; 90,81</t>
+          <t>81,47; 90,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,54; 84,96</t>
+          <t>74,84; 85,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,67; 95,87</t>
+          <t>89,04; 95,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,16; 97,84</t>
+          <t>90,61; 96,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,24; 66,52</t>
+          <t>56,85; 66,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,66; 60,37</t>
+          <t>50,84; 60,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71,49; 79,4</t>
+          <t>71,75; 79,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,86; 95,37</t>
+          <t>88,65; 93,76</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,88; 32,67</t>
+          <t>21,86; 32,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,12; 49,64</t>
+          <t>38,06; 50,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,87; 50,21</t>
+          <t>38,11; 49,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71,83; 81,54</t>
+          <t>72,52; 81,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,05; 91,23</t>
+          <t>82,91; 90,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,92; 89,99</t>
+          <t>81,81; 89,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,94; 91,6</t>
+          <t>83,0; 91,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,98; 94,07</t>
+          <t>89,1; 93,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,28; 61,59</t>
+          <t>53,06; 61,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60,9; 69,34</t>
+          <t>60,83; 69,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,17; 70,52</t>
+          <t>61,96; 70,17</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>81,37; 86,84</t>
+          <t>81,4; 86,71</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,56; 44,62</t>
+          <t>36,95; 44,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,8; 50,35</t>
+          <t>42,14; 49,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,13; 56,48</t>
+          <t>48,62; 56,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68,32; 76,97</t>
+          <t>68,31; 76,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,68; 88,86</t>
+          <t>83,69; 88,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,21; 85,54</t>
+          <t>79,39; 85,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,18; 89,25</t>
+          <t>83,91; 89,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>86,55; 95,75</t>
+          <t>84,86; 90,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61,22; 66,66</t>
+          <t>61,42; 66,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61,44; 67,04</t>
+          <t>61,62; 67,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67,52; 72,72</t>
+          <t>67,77; 72,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,0; 89,27</t>
+          <t>77,81; 82,52</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,49; 34,79</t>
+          <t>27,54; 34,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,07; 50,68</t>
+          <t>42,66; 50,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,75; 62,19</t>
+          <t>54,86; 61,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,31; 44,6</t>
+          <t>39,96; 47,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>78,96; 84,41</t>
+          <t>78,99; 84,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,07; 85,33</t>
+          <t>80,01; 85,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,63; 89,55</t>
+          <t>84,79; 89,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,73; 94,72</t>
+          <t>90,37; 94,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,51; 59,62</t>
+          <t>54,29; 59,45</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62,57; 67,94</t>
+          <t>62,98; 67,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70,87; 75,46</t>
+          <t>70,95; 75,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,26; 69,47</t>
+          <t>66,06; 70,84</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32,51; 35,96</t>
+          <t>32,5; 35,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,96; 45,53</t>
+          <t>41,96; 45,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,22; 54,83</t>
+          <t>51,19; 54,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46,73; 66,57</t>
+          <t>63,75; 67,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>82,71; 85,26</t>
+          <t>82,87; 85,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,28; 84,92</t>
+          <t>82,2; 84,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,21; 88,58</t>
+          <t>86,31; 88,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>90,37; 93,12</t>
+          <t>89,56; 91,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58,32; 60,8</t>
+          <t>58,33; 60,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62,82; 65,2</t>
+          <t>62,81; 65,2</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69,55; 71,68</t>
+          <t>69,58; 71,79</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>68,12; 80,32</t>
+          <t>77,31; 79,47</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186588</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>264925</t>
+          <t>290022</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>451513</t>
+          <t>473523</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88710; 121924</t>
+          <t>88095; 120554</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>119673; 154966</t>
+          <t>117689; 153959</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134189; 169319</t>
+          <t>132422; 167308</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>167074; 206429</t>
+          <t>165114; 201308</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>203968; 228161</t>
+          <t>203578; 228211</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>237347; 260528</t>
+          <t>236410; 260575</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>245393; 267531</t>
+          <t>246261; 269239</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249691; 273876</t>
+          <t>277295; 298652</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>298938; 344410</t>
+          <t>297710; 344470</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>364556; 410673</t>
+          <t>362281; 408550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>385562; 432174</t>
+          <t>387611; 430516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>427060; 474473</t>
+          <t>449896; 493567</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375996</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>471212</t>
+          <t>497943</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>847208</t>
+          <t>886854</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>165735; 210854</t>
+          <t>167283; 212371</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>169157; 210732</t>
+          <t>168039; 213461</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213820; 259980</t>
+          <t>214137; 258659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>346819; 401491</t>
+          <t>361875; 414307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>405116; 436712</t>
+          <t>404624; 437175</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>419933; 456415</t>
+          <t>419645; 454839</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>430915; 464124</t>
+          <t>432639; 465467</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>455200; 483614</t>
+          <t>479610; 511814</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>575021; 641642</t>
+          <t>579632; 638143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>598672; 663053</t>
+          <t>591206; 659402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>651498; 712384</t>
+          <t>652069; 715106</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>812061; 877282</t>
+          <t>852899; 915286</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>240290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>311471</t>
+          <t>318735</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>553619</t>
+          <t>559025</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75989; 107839</t>
+          <t>75904; 110208</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>117293; 151427</t>
+          <t>117509; 151982</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170705; 203458</t>
+          <t>170168; 204025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227949; 255290</t>
+          <t>225113; 252900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>264740; 291772</t>
+          <t>264653; 291601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>271863; 298588</t>
+          <t>271319; 298159</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>290298; 312225</t>
+          <t>289913; 311951</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>300583; 320661</t>
+          <t>308112; 327186</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>343511; 393732</t>
+          <t>343051; 393897</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>394989; 447831</t>
+          <t>393865; 443833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>469817; 511374</t>
+          <t>467917; 509988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>534332; 569993</t>
+          <t>540830; 576194</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202930</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>430401</t>
+          <t>372803</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>633330</t>
+          <t>613715</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90842; 127360</t>
+          <t>91253; 127094</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162551; 202510</t>
+          <t>162375; 201539</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171107; 209321</t>
+          <t>171494; 210734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>179981; 223721</t>
+          <t>214471; 265382</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>288633; 318597</t>
+          <t>290940; 317114</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>308387; 338586</t>
+          <t>308584; 338642</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>304871; 335372</t>
+          <t>304627; 336154</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>409158; 449595</t>
+          <t>353270; 386126</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>387688; 441154</t>
+          <t>388011; 442024</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>479846; 534137</t>
+          <t>480565; 531232</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>486582; 536939</t>
+          <t>485024; 536059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>598681; 675463</t>
+          <t>581237; 643085</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>180895</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>247405</t>
+          <t>216270</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>404498</t>
+          <t>397164</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>59957; 87974</t>
+          <t>58439; 86750</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51241; 79064</t>
+          <t>52526; 80015</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107188; 136300</t>
+          <t>106604; 134875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>149298; 163448</t>
+          <t>171601; 187858</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>169520; 188585</t>
+          <t>169188; 188378</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>163675; 186554</t>
+          <t>164342; 187327</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>192972; 208648</t>
+          <t>193776; 208904</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>238500; 253181</t>
+          <t>207422; 221388</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>235236; 273386</t>
+          <t>233654; 274628</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>218965; 260935</t>
+          <t>219718; 262715</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>306570; 340528</t>
+          <t>307699; 342238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>392750; 416839</t>
+          <t>384815; 407013</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207574</t>
+          <t>209402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>235819</t>
+          <t>242112</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>443393</t>
+          <t>451515</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59244; 88462</t>
+          <t>59211; 88866</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>101710; 136001</t>
+          <t>104284; 137195</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>99018; 131297</t>
+          <t>99652; 130620</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>193669; 219858</t>
+          <t>196326; 220581</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>231006; 253765</t>
+          <t>230617; 253073</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>229401; 252000</t>
+          <t>229104; 251627</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>225661; 249212</t>
+          <t>225832; 249181</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>228734; 241805</t>
+          <t>235011; 247694</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>292495; 338093</t>
+          <t>291295; 338655</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>337398; 384177</t>
+          <t>337020; 384314</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>331720; 376250</t>
+          <t>330588; 374424</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>428595; 457375</t>
+          <t>435028; 463444</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>452810</t>
+          <t>522928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>769182</t>
+          <t>677877</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1221992</t>
+          <t>1200804</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>224878; 274426</t>
+          <t>227270; 276481</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>277016; 333735</t>
+          <t>279318; 329710</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>315510; 370261</t>
+          <t>318723; 371831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>426531; 480536</t>
+          <t>491654; 550133</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>532068; 564983</t>
+          <t>532117; 563545</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>549614; 593526</t>
+          <t>550821; 592445</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>580253; 615174</t>
+          <t>578368; 616318</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>735039; 813207</t>
+          <t>655192; 695503</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>765742; 833868</t>
+          <t>768327; 833691</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>833487; 909502</t>
+          <t>835928; 910900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>907922; 977889</t>
+          <t>911405; 979057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1164053; 1315381</t>
+          <t>1160707; 1231060</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>295470</t>
+          <t>345719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>667162</t>
+          <t>770160</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>962632</t>
+          <t>1115880</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>204202; 258484</t>
+          <t>204583; 256058</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>335549; 394881</t>
+          <t>332344; 392438</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>426311; 484187</t>
+          <t>427114; 481842</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>132880; 414247</t>
+          <t>318914; 377711</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>618632; 661390</t>
+          <t>618867; 661230</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>658084; 701322</t>
+          <t>657559; 703135</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>699215; 739828</t>
+          <t>700486; 739088</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>651164; 679863</t>
+          <t>751254; 785598</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>832044; 909991</t>
+          <t>828681; 907526</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1001669; 1087628</t>
+          <t>1008253; 1085134</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1137210; 1210880</t>
+          <t>1138641; 1209670</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>596991; 1143817</t>
+          <t>1076302; 1154283</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1064943; 1177799</t>
+          <t>1064692; 1178098</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1437310; 1559799</t>
+          <t>1437562; 1557613</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1734100; 1856067</t>
+          <t>1732899; 1853887</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1616269; 2302431</t>
+          <t>2251481; 2374350</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2791090; 2877241</t>
+          <t>2796494; 2881418</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2926098; 3019903</t>
+          <t>2923419; 3017987</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3051482; 3135285</t>
+          <t>3055023; 3134357</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3353826; 3455773</t>
+          <t>3345644; 3421280</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3878149; 4043597</t>
+          <t>3879112; 4037308</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4386140; 4552176</t>
+          <t>4385240; 4552131</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4816483; 4963963</t>
+          <t>4818389; 4971138</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4883769; 5758566</t>
+          <t>5618246; 5775071</t>
         </is>
       </c>
     </row>
